--- a/cet4/result/87_医道女神_生命守护的传奇/87_医道女神_生命守护的传奇_学习版.xlsx
+++ b/cet4/result/87_医道女神_生命守护的传奇/87_医道女神_生命守护的传奇_学习版.xlsx
@@ -397,745 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>doctor</v>
       </c>
       <c r="B2" t="str">
-        <v>doctor</v>
+        <v>/ˈdɑːktər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>医生</v>
       </c>
-      <c r="D2" t="str">
-        <v>doctor(医生)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>sample</v>
       </c>
       <c r="B3" t="str">
-        <v>sample</v>
+        <v>/ˈsæmpl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>样本</v>
       </c>
-      <c r="D3" t="str">
-        <v>sample(样本)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>between</v>
       </c>
       <c r="B4" t="str">
-        <v>between</v>
+        <v>/bɪˈtwiːn/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D4" t="str">
         <v>在...之间</v>
       </c>
-      <c r="D4" t="str">
-        <v>between(在...之间)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>cow</v>
       </c>
       <c r="B5" t="str">
-        <v>cow</v>
+        <v>/kaʊ/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>奶牛</v>
       </c>
-      <c r="D5" t="str">
-        <v>cow(奶牛)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>menu</v>
       </c>
       <c r="B6" t="str">
-        <v>menu</v>
+        <v>/ˈmenjuː/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>菜单</v>
       </c>
-      <c r="D6" t="str">
-        <v>menu(菜单)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>descend</v>
       </c>
       <c r="B7" t="str">
-        <v>descend</v>
+        <v>/dɪˈsend/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>下降</v>
       </c>
-      <c r="D7" t="str">
-        <v>descend(下降)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>day</v>
       </c>
       <c r="B8" t="str">
-        <v>day</v>
+        <v>/deɪ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>一天</v>
       </c>
-      <c r="D8" t="str">
-        <v>day(一天)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>freight</v>
       </c>
       <c r="B9" t="str">
-        <v>freight</v>
+        <v>/freɪt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>货运</v>
       </c>
-      <c r="D9" t="str">
-        <v>freight(货运)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>booth</v>
       </c>
       <c r="B10" t="str">
-        <v>booth</v>
+        <v>/buːθ/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>电话亭</v>
       </c>
-      <c r="D10" t="str">
-        <v>booth(电话亭)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>satisfaction</v>
       </c>
       <c r="B11" t="str">
-        <v>satisfaction</v>
+        <v>/ˌsætɪsˈfækʃn/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>满意</v>
       </c>
-      <c r="D11" t="str">
-        <v>satisfaction(满意)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>loose</v>
       </c>
       <c r="B12" t="str">
-        <v>loose</v>
+        <v>/luːs/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>松了</v>
       </c>
-      <c r="D12" t="str">
-        <v>loose(松了)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>loaf</v>
       </c>
       <c r="B13" t="str">
-        <v>loaf</v>
+        <v>/loʊf/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>面包</v>
       </c>
-      <c r="D13" t="str">
-        <v>loaf(面包)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>brass</v>
       </c>
       <c r="B14" t="str">
-        <v>brass</v>
+        <v>/bræs/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>黄铜</v>
       </c>
-      <c r="D14" t="str">
-        <v>brass(黄铜)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>attention</v>
       </c>
       <c r="B15" t="str">
-        <v>attention</v>
+        <v>/əˈtenʃn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>注意</v>
       </c>
-      <c r="D15" t="str">
-        <v>attention(注意)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>faint</v>
       </c>
       <c r="B16" t="str">
-        <v>faint</v>
+        <v>/feɪnt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>微弱</v>
       </c>
-      <c r="D16" t="str">
-        <v>faint(微弱)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>terrible</v>
       </c>
       <c r="B17" t="str">
-        <v>terrible</v>
+        <v>/ˈterəbl/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>可怕的</v>
       </c>
-      <c r="D17" t="str">
-        <v>terrible(可怕的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>moan</v>
       </c>
       <c r="B18" t="str">
-        <v>moan</v>
+        <v>/moʊn/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>呻吟</v>
       </c>
-      <c r="D18" t="str">
-        <v>moan(呻吟)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>spear</v>
       </c>
       <c r="B19" t="str">
-        <v>spear</v>
+        <v>/spɪr/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>矛状物</v>
       </c>
-      <c r="D19" t="str">
-        <v>spear(矛状物)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>instruction</v>
       </c>
       <c r="B20" t="str">
-        <v>instruction</v>
+        <v>/ɪnˈstrʌkʃn/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>指示</v>
       </c>
-      <c r="D20" t="str">
-        <v>instruction(指示)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>operational</v>
       </c>
       <c r="B21" t="str">
-        <v>operational</v>
+        <v>/ˌɑːpəˈreɪʃənl/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>可操作的</v>
       </c>
-      <c r="D21" t="str">
-        <v>operational(可操作的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>mature</v>
       </c>
       <c r="B22" t="str">
-        <v>mature</v>
+        <v>/məˈtʃʊr,məˈtʊr/</v>
       </c>
       <c r="C22" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>成熟</v>
       </c>
-      <c r="D22" t="str">
-        <v>mature(成熟)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>port</v>
       </c>
       <c r="B23" t="str">
-        <v>port</v>
+        <v>/pɔːrt/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>港口</v>
       </c>
-      <c r="D23" t="str">
-        <v>port(港口)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>session</v>
       </c>
       <c r="B24" t="str">
-        <v>session</v>
+        <v>/ˈseʃn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>会议</v>
       </c>
-      <c r="D24" t="str">
-        <v>session(会议)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>correct</v>
       </c>
       <c r="B25" t="str">
-        <v>correct</v>
+        <v>/kəˈrekt/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>正确</v>
       </c>
-      <c r="D25" t="str">
-        <v>correct(正确)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>liquid</v>
       </c>
       <c r="B26" t="str">
-        <v>liquid</v>
+        <v>/ˈlɪkwɪd/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>液体</v>
       </c>
-      <c r="D26" t="str">
-        <v>liquid(液体)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>determine</v>
       </c>
       <c r="B27" t="str">
-        <v>determine</v>
+        <v>/dɪˈtɜːrmɪn/</v>
       </c>
       <c r="C27" t="str">
+        <v>vt./vi./v.</v>
+      </c>
+      <c r="D27" t="str">
         <v>决定</v>
       </c>
-      <c r="D27" t="str">
-        <v>determine(决定)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>somewhat</v>
       </c>
       <c r="B28" t="str">
-        <v>somewhat</v>
+        <v>/ˈsʌmwʌt/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./v./adv./pron.</v>
+      </c>
+      <c r="D28" t="str">
         <v>有点</v>
       </c>
-      <c r="D28" t="str">
-        <v>somewhat(有点)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>cunning</v>
       </c>
       <c r="B29" t="str">
-        <v>cunning</v>
+        <v>/ˈkʌnɪŋ/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>狡猾的</v>
       </c>
-      <c r="D29" t="str">
-        <v>cunning(狡猾的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>impact</v>
       </c>
       <c r="B30" t="str">
-        <v>impact</v>
+        <v>/ˈɪmpækt/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>影响</v>
       </c>
-      <c r="D30" t="str">
-        <v>impact(影响)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>note</v>
       </c>
       <c r="B31" t="str">
-        <v>note</v>
+        <v>/noʊt/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D31" t="str">
         <v>笔记</v>
       </c>
-      <c r="D31" t="str">
-        <v>note(笔记)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>circle</v>
       </c>
       <c r="B32" t="str">
-        <v>circle</v>
+        <v>/ˈsɜːrkl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>循环</v>
       </c>
-      <c r="D32" t="str">
-        <v>circle(循环)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>see</v>
       </c>
       <c r="B33" t="str">
-        <v>see</v>
+        <v>/siː/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D33" t="str">
         <v>看到</v>
       </c>
-      <c r="D33" t="str">
-        <v>see(看到)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>depress</v>
       </c>
       <c r="B34" t="str">
-        <v>depress</v>
+        <v>/dɪˈpres/</v>
       </c>
       <c r="C34" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D34" t="str">
         <v>沮丧</v>
       </c>
-      <c r="D34" t="str">
-        <v>depress(沮丧)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>speciality</v>
       </c>
       <c r="B35" t="str">
-        <v>speciality</v>
+        <v>/ˌspeʃiˈæləti/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>专家</v>
       </c>
-      <c r="D35" t="str">
-        <v>speciality(专家)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>climb</v>
       </c>
       <c r="B36" t="str">
-        <v>climb</v>
+        <v>/klaɪm/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D36" t="str">
         <v>攀登</v>
       </c>
-      <c r="D36" t="str">
-        <v>climb(攀登)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>faculty</v>
       </c>
       <c r="B37" t="str">
-        <v>faculty</v>
+        <v>/ˈfæklti/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>全体教员</v>
       </c>
-      <c r="D37" t="str">
-        <v>faculty(全体教员)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>stuff</v>
       </c>
       <c r="B38" t="str">
-        <v>stuff</v>
+        <v>/stʌf/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D38" t="str">
         <v>资料</v>
       </c>
-      <c r="D38" t="str">
-        <v>stuff(资料)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>slit</v>
       </c>
       <c r="B39" t="str">
-        <v>slit</v>
+        <v>/slɪt/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D39" t="str">
         <v>裂缝</v>
       </c>
-      <c r="D39" t="str">
-        <v>slit(裂缝)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>design</v>
       </c>
       <c r="B40" t="str">
-        <v>design</v>
+        <v>/dɪˈzaɪn/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D40" t="str">
         <v>设计</v>
       </c>
-      <c r="D40" t="str">
-        <v>design(设计)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>thread</v>
       </c>
       <c r="B41" t="str">
-        <v>doctor</v>
+        <v>/θred/</v>
       </c>
       <c r="C41" t="str">
-        <v>医生</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>doctor(医生)📢</v>
+        <v>线</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>read</v>
       </c>
       <c r="B42" t="str">
-        <v>thread</v>
+        <v>/riːd/</v>
       </c>
       <c r="C42" t="str">
-        <v>线</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>thread(线)📢</v>
+        <v>阅读</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>slave</v>
       </c>
       <c r="B43" t="str">
-        <v>read</v>
+        <v>/sleɪv/</v>
       </c>
       <c r="C43" t="str">
-        <v>阅读</v>
+        <v>n./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>read(阅读)📢</v>
+        <v>奴隶</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>cat</v>
       </c>
       <c r="B44" t="str">
-        <v>slave</v>
+        <v>/kæt/</v>
       </c>
       <c r="C44" t="str">
-        <v>奴隶</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>slave(奴隶)📢</v>
+        <v>猫</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>herd</v>
       </c>
       <c r="B45" t="str">
-        <v>cat</v>
+        <v>/hɜːrd/</v>
       </c>
       <c r="C45" t="str">
-        <v>猫</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>cat(猫)📢</v>
+        <v>群</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>scope</v>
       </c>
       <c r="B46" t="str">
-        <v>herd</v>
+        <v>/skoʊp/</v>
       </c>
       <c r="C46" t="str">
-        <v>群</v>
+        <v>n./vt.</v>
       </c>
       <c r="D46" t="str">
-        <v>herd(群)📢</v>
+        <v>范围</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>criminal</v>
       </c>
       <c r="B47" t="str">
-        <v>scope</v>
+        <v>/ˈkrɪmɪnl/</v>
       </c>
       <c r="C47" t="str">
-        <v>范围</v>
+        <v>n./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>scope(范围)📢</v>
+        <v>罪犯</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>invent</v>
       </c>
       <c r="B48" t="str">
-        <v>criminal</v>
+        <v>/ɪnˈvent/</v>
       </c>
       <c r="C48" t="str">
-        <v>罪犯</v>
+        <v>vt.</v>
       </c>
       <c r="D48" t="str">
-        <v>criminal(罪犯)📢</v>
+        <v>发明</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>hello</v>
       </c>
       <c r="B49" t="str">
-        <v>invent</v>
+        <v>/həˈləʊ/</v>
       </c>
       <c r="C49" t="str">
-        <v>发明</v>
+        <v>n./int.</v>
       </c>
       <c r="D49" t="str">
-        <v>invent(发明)📢</v>
+        <v>你好</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>ambulance</v>
       </c>
       <c r="B50" t="str">
-        <v>hello</v>
+        <v>/ˈæmbjələns/</v>
       </c>
       <c r="C50" t="str">
-        <v>你好</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>hello(你好)📢</v>
+        <v>救护车</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>address</v>
       </c>
       <c r="B51" t="str">
-        <v>ambulance</v>
+        <v>/əˈdres,ˈædres/</v>
       </c>
       <c r="C51" t="str">
-        <v>救护车</v>
+        <v>n./vt.</v>
       </c>
       <c r="D51" t="str">
-        <v>ambulance(救护车)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>address</v>
-      </c>
-      <c r="C52" t="str">
         <v>地址</v>
-      </c>
-      <c r="D52" t="str">
-        <v>address(地址)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>